--- a/outputs/table/table3_sensitivity_specificity.xlsx
+++ b/outputs/table/table3_sensitivity_specificity.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="127">
   <si>
     <t>Outcome</t>
   </si>
@@ -70,343 +70,331 @@
     <t>External</t>
   </si>
   <si>
-    <t>1088 (329)</t>
-  </si>
-  <si>
-    <t>925 (425)</t>
-  </si>
-  <si>
-    <t>1088 (204)</t>
-  </si>
-  <si>
-    <t>925 (285)</t>
-  </si>
-  <si>
-    <t>1088 (83)</t>
-  </si>
-  <si>
-    <t>925 (168)</t>
-  </si>
-  <si>
-    <t>0.808</t>
-  </si>
-  <si>
-    <t>0.714</t>
-  </si>
-  <si>
-    <t>0.813</t>
+    <t>1259 (385)</t>
+  </si>
+  <si>
+    <t>1123 (507)</t>
+  </si>
+  <si>
+    <t>1259 (232)</t>
+  </si>
+  <si>
+    <t>1123 (335)</t>
+  </si>
+  <si>
+    <t>1259 (105)</t>
+  </si>
+  <si>
+    <t>1123 (188)</t>
+  </si>
+  <si>
+    <t>0.795</t>
   </si>
   <si>
     <t>0.718</t>
   </si>
   <si>
-    <t>0.818</t>
-  </si>
-  <si>
-    <t>0.731</t>
-  </si>
-  <si>
-    <t>0.728</t>
-  </si>
-  <si>
-    <t>0.820</t>
-  </si>
-  <si>
-    <t>0.734</t>
-  </si>
-  <si>
-    <t>0.727</t>
-  </si>
-  <si>
-    <t>0.662</t>
-  </si>
-  <si>
-    <t>0.726</t>
-  </si>
-  <si>
-    <t>0.663</t>
-  </si>
-  <si>
-    <t>0.748</t>
-  </si>
-  <si>
-    <t>0.699</t>
-  </si>
-  <si>
-    <t>0.674</t>
-  </si>
-  <si>
-    <t>0.746</t>
-  </si>
-  <si>
-    <t>0.792</t>
-  </si>
-  <si>
-    <t>0.621</t>
-  </si>
-  <si>
-    <t>0.798</t>
-  </si>
-  <si>
-    <t>0.613</t>
-  </si>
-  <si>
-    <t>0.809</t>
-  </si>
-  <si>
-    <t>0.643</t>
-  </si>
-  <si>
-    <t>0.806</t>
+    <t>0.796</t>
+  </si>
+  <si>
+    <t>0.802</t>
+  </si>
+  <si>
+    <t>0.730</t>
   </si>
   <si>
     <t>0.811</t>
   </si>
   <si>
-    <t>0.637</t>
-  </si>
-  <si>
-    <t>73.6%</t>
-  </si>
-  <si>
-    <t>68.5%</t>
-  </si>
-  <si>
-    <t>73.3%</t>
+    <t>0.810</t>
+  </si>
+  <si>
+    <t>0.733</t>
+  </si>
+  <si>
+    <t>0.722</t>
+  </si>
+  <si>
+    <t>0.665</t>
+  </si>
+  <si>
+    <t>0.721</t>
+  </si>
+  <si>
+    <t>0.741</t>
+  </si>
+  <si>
+    <t>0.681</t>
+  </si>
+  <si>
+    <t>0.723</t>
+  </si>
+  <si>
+    <t>0.677</t>
+  </si>
+  <si>
+    <t>0.735</t>
+  </si>
+  <si>
+    <t>0.686</t>
+  </si>
+  <si>
+    <t>0.768</t>
+  </si>
+  <si>
+    <t>0.616</t>
+  </si>
+  <si>
+    <t>0.614</t>
+  </si>
+  <si>
+    <t>0.772</t>
+  </si>
+  <si>
+    <t>0.630</t>
+  </si>
+  <si>
+    <t>0.770</t>
+  </si>
+  <si>
+    <t>0.617</t>
+  </si>
+  <si>
+    <t>0.773</t>
+  </si>
+  <si>
+    <t>0.627</t>
+  </si>
+  <si>
+    <t>81.6%</t>
+  </si>
+  <si>
+    <t>78.1%</t>
+  </si>
+  <si>
+    <t>70.6%</t>
+  </si>
+  <si>
+    <t>55.8%</t>
+  </si>
+  <si>
+    <t>73.8%</t>
+  </si>
+  <si>
+    <t>61.1%</t>
+  </si>
+  <si>
+    <t>83.9%</t>
+  </si>
+  <si>
+    <t>78.5%</t>
+  </si>
+  <si>
+    <t>87.3%</t>
+  </si>
+  <si>
+    <t>80.1%</t>
+  </si>
+  <si>
+    <t>83.2%</t>
+  </si>
+  <si>
+    <t>76.7%</t>
+  </si>
+  <si>
+    <t>78.4%</t>
+  </si>
+  <si>
+    <t>72.5%</t>
+  </si>
+  <si>
+    <t>83.6%</t>
+  </si>
+  <si>
+    <t>78.9%</t>
+  </si>
+  <si>
+    <t>74.9%</t>
+  </si>
+  <si>
+    <t>77.6%</t>
+  </si>
+  <si>
+    <t>80.0%</t>
+  </si>
+  <si>
+    <t>81.9%</t>
+  </si>
+  <si>
+    <t>66.5%</t>
+  </si>
+  <si>
+    <t>72.4%</t>
+  </si>
+  <si>
+    <t>46.8%</t>
+  </si>
+  <si>
+    <t>84.8%</t>
+  </si>
+  <si>
+    <t>68.6%</t>
+  </si>
+  <si>
+    <t>79.0%</t>
+  </si>
+  <si>
+    <t>58.5%</t>
+  </si>
+  <si>
+    <t>67.6%</t>
+  </si>
+  <si>
+    <t>65.1%</t>
+  </si>
+  <si>
+    <t>55.5%</t>
+  </si>
+  <si>
+    <t>75.6%</t>
+  </si>
+  <si>
+    <t>75.5%</t>
+  </si>
+  <si>
+    <t>72.0%</t>
+  </si>
+  <si>
+    <t>71.8%</t>
+  </si>
+  <si>
+    <t>65.0%</t>
+  </si>
+  <si>
+    <t>56.0%</t>
+  </si>
+  <si>
+    <t>59.6%</t>
+  </si>
+  <si>
+    <t>51.3%</t>
+  </si>
+  <si>
+    <t>52.8%</t>
+  </si>
+  <si>
+    <t>43.8%</t>
+  </si>
+  <si>
+    <t>58.4%</t>
+  </si>
+  <si>
+    <t>51.0%</t>
   </si>
   <si>
     <t>54.4%</t>
   </si>
   <si>
-    <t>78.4%</t>
-  </si>
-  <si>
-    <t>67.1%</t>
-  </si>
-  <si>
-    <t>82.7%</t>
-  </si>
-  <si>
-    <t>80.0%</t>
-  </si>
-  <si>
-    <t>83.9%</t>
-  </si>
-  <si>
-    <t>77.4%</t>
-  </si>
-  <si>
-    <t>75.5%</t>
-  </si>
-  <si>
-    <t>70.5%</t>
-  </si>
-  <si>
-    <t>75.0%</t>
-  </si>
-  <si>
-    <t>64.9%</t>
-  </si>
-  <si>
-    <t>80.4%</t>
-  </si>
-  <si>
-    <t>80.7%</t>
-  </si>
-  <si>
-    <t>76.5%</t>
-  </si>
-  <si>
-    <t>74.0%</t>
-  </si>
-  <si>
-    <t>79.4%</t>
-  </si>
-  <si>
-    <t>81.1%</t>
-  </si>
-  <si>
-    <t>84.3%</t>
-  </si>
-  <si>
-    <t>69.0%</t>
-  </si>
-  <si>
-    <t>78.3%</t>
-  </si>
-  <si>
-    <t>42.3%</t>
-  </si>
-  <si>
-    <t>90.4%</t>
-  </si>
-  <si>
-    <t>63.7%</t>
-  </si>
-  <si>
-    <t>85.5%</t>
-  </si>
-  <si>
-    <t>91.6%</t>
-  </si>
-  <si>
-    <t>75.1%</t>
-  </si>
-  <si>
-    <t>65.4%</t>
-  </si>
-  <si>
-    <t>75.9%</t>
-  </si>
-  <si>
-    <t>74.6%</t>
-  </si>
-  <si>
-    <t>71.4%</t>
-  </si>
-  <si>
-    <t>69.4%</t>
-  </si>
-  <si>
-    <t>67.2%</t>
-  </si>
-  <si>
-    <t>54.8%</t>
-  </si>
-  <si>
-    <t>65.0%</t>
-  </si>
-  <si>
-    <t>58.8%</t>
+    <t>36.0%</t>
+  </si>
+  <si>
+    <t>57.3%</t>
+  </si>
+  <si>
+    <t>49.6%</t>
+  </si>
+  <si>
+    <t>43.0%</t>
+  </si>
+  <si>
+    <t>61.7%</t>
+  </si>
+  <si>
+    <t>71.1%</t>
+  </si>
+  <si>
+    <t>66.7%</t>
+  </si>
+  <si>
+    <t>47.8%</t>
+  </si>
+  <si>
+    <t>66.6%</t>
+  </si>
+  <si>
+    <t>56.8%</t>
   </si>
   <si>
     <t>62.0%</t>
   </si>
   <si>
-    <t>53.1%</t>
-  </si>
-  <si>
-    <t>61.8%</t>
-  </si>
-  <si>
-    <t>59.5%</t>
-  </si>
-  <si>
-    <t>60.1%</t>
-  </si>
-  <si>
-    <t>50.8%</t>
-  </si>
-  <si>
-    <t>60.4%</t>
-  </si>
-  <si>
-    <t>51.6%</t>
-  </si>
-  <si>
-    <t>60.6%</t>
-  </si>
-  <si>
-    <t>49.4%</t>
-  </si>
-  <si>
-    <t>61.1%</t>
-  </si>
-  <si>
-    <t>50.1%</t>
-  </si>
-  <si>
-    <t>69.6%</t>
-  </si>
-  <si>
-    <t>59.9%</t>
-  </si>
-  <si>
-    <t>54.2%</t>
-  </si>
-  <si>
-    <t>64.8%</t>
-  </si>
-  <si>
-    <t>48.5%</t>
-  </si>
-  <si>
-    <t>62.2%</t>
-  </si>
-  <si>
-    <t>49.0%</t>
-  </si>
-  <si>
-    <t>66.8%</t>
-  </si>
-  <si>
-    <t>65.3%</t>
-  </si>
-  <si>
-    <t>73.5%</t>
-  </si>
-  <si>
-    <t>68.3%</t>
-  </si>
-  <si>
-    <t>71.9%</t>
-  </si>
-  <si>
-    <t>66.4%</t>
-  </si>
-  <si>
-    <t>70.7%</t>
-  </si>
-  <si>
-    <t>67.4%</t>
-  </si>
-  <si>
-    <t>64.5%</t>
-  </si>
-  <si>
-    <t>58.5%</t>
-  </si>
-  <si>
-    <t>64.2%</t>
+    <t>70.1%</t>
+  </si>
+  <si>
+    <t>65.7%</t>
+  </si>
+  <si>
+    <t>74.1%</t>
+  </si>
+  <si>
+    <t>67.0%</t>
+  </si>
+  <si>
+    <t>70.8%</t>
+  </si>
+  <si>
+    <t>66.2%</t>
+  </si>
+  <si>
+    <t>68.1%</t>
+  </si>
+  <si>
+    <t>64.3%</t>
+  </si>
+  <si>
+    <t>53.6%</t>
+  </si>
+  <si>
+    <t>62.1%</t>
+  </si>
+  <si>
+    <t>57.4%</t>
+  </si>
+  <si>
+    <t>59.8%</t>
+  </si>
+  <si>
+    <t>50.3%</t>
   </si>
   <si>
     <t>61.2%</t>
   </si>
   <si>
-    <t>63.9%</t>
-  </si>
-  <si>
-    <t>60.0%</t>
+    <t>57.2%</t>
+  </si>
+  <si>
+    <t>62.9%</t>
+  </si>
+  <si>
+    <t>54.1%</t>
   </si>
   <si>
     <t>63.4%</t>
   </si>
   <si>
-    <t>59.1%</t>
-  </si>
-  <si>
-    <t>62.9%</t>
-  </si>
-  <si>
-    <t>53.5%</t>
-  </si>
-  <si>
-    <t>70.2%</t>
-  </si>
-  <si>
-    <t>64.6%</t>
-  </si>
-  <si>
-    <t>55.9%</t>
-  </si>
-  <si>
-    <t>52.1%</t>
-  </si>
-  <si>
-    <t>64.4%</t>
-  </si>
-  <si>
-    <t>52.5%</t>
+    <t>71.2%</t>
+  </si>
+  <si>
+    <t>67.7%</t>
+  </si>
+  <si>
+    <t>57.1%</t>
+  </si>
+  <si>
+    <t>63.6%</t>
+  </si>
+  <si>
+    <t>51.1%</t>
   </si>
 </sst>
 </file>
@@ -816,7 +804,7 @@
         <v>78</v>
       </c>
       <c r="H2" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -842,7 +830,7 @@
         <v>79</v>
       </c>
       <c r="H3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -868,7 +856,7 @@
         <v>80</v>
       </c>
       <c r="H4" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -885,7 +873,7 @@
         <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F5" t="s">
         <v>53</v>
@@ -894,7 +882,7 @@
         <v>81</v>
       </c>
       <c r="H5" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -911,7 +899,7 @@
         <v>18</v>
       </c>
       <c r="E6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F6" t="s">
         <v>54</v>
@@ -920,7 +908,7 @@
         <v>82</v>
       </c>
       <c r="H6" t="s">
-        <v>109</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -937,7 +925,7 @@
         <v>19</v>
       </c>
       <c r="E7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F7" t="s">
         <v>55</v>
@@ -946,7 +934,7 @@
         <v>83</v>
       </c>
       <c r="H7" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -963,7 +951,7 @@
         <v>18</v>
       </c>
       <c r="E8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F8" t="s">
         <v>56</v>
@@ -972,7 +960,7 @@
         <v>84</v>
       </c>
       <c r="H8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -989,7 +977,7 @@
         <v>19</v>
       </c>
       <c r="E9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F9" t="s">
         <v>57</v>
@@ -998,7 +986,7 @@
         <v>85</v>
       </c>
       <c r="H9" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1015,7 +1003,7 @@
         <v>18</v>
       </c>
       <c r="E10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F10" t="s">
         <v>58</v>
@@ -1024,7 +1012,7 @@
         <v>86</v>
       </c>
       <c r="H10" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1041,7 +1029,7 @@
         <v>19</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F11" t="s">
         <v>59</v>
@@ -1050,7 +1038,7 @@
         <v>87</v>
       </c>
       <c r="H11" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1067,7 +1055,7 @@
         <v>20</v>
       </c>
       <c r="E12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F12" t="s">
         <v>60</v>
@@ -1076,7 +1064,7 @@
         <v>88</v>
       </c>
       <c r="H12" t="s">
-        <v>115</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1093,7 +1081,7 @@
         <v>21</v>
       </c>
       <c r="E13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F13" t="s">
         <v>61</v>
@@ -1102,7 +1090,7 @@
         <v>89</v>
       </c>
       <c r="H13" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1119,7 +1107,7 @@
         <v>20</v>
       </c>
       <c r="E14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F14" t="s">
         <v>62</v>
@@ -1128,7 +1116,7 @@
         <v>90</v>
       </c>
       <c r="H14" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1145,7 +1133,7 @@
         <v>21</v>
       </c>
       <c r="E15" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F15" t="s">
         <v>63</v>
@@ -1154,7 +1142,7 @@
         <v>91</v>
       </c>
       <c r="H15" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1171,7 +1159,7 @@
         <v>20</v>
       </c>
       <c r="E16" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F16" t="s">
         <v>64</v>
@@ -1180,7 +1168,7 @@
         <v>92</v>
       </c>
       <c r="H16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1197,16 +1185,16 @@
         <v>21</v>
       </c>
       <c r="E17" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F17" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="G17" t="s">
         <v>93</v>
       </c>
       <c r="H17" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1223,16 +1211,16 @@
         <v>20</v>
       </c>
       <c r="E18" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G18" t="s">
         <v>94</v>
       </c>
       <c r="H18" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1249,16 +1237,16 @@
         <v>21</v>
       </c>
       <c r="E19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G19" t="s">
         <v>95</v>
       </c>
       <c r="H19" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1275,16 +1263,16 @@
         <v>20</v>
       </c>
       <c r="E20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G20" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="H20" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1301,16 +1289,16 @@
         <v>21</v>
       </c>
       <c r="E21" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G21" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H21" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1330,13 +1318,13 @@
         <v>41</v>
       </c>
       <c r="F22" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H22" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1356,13 +1344,13 @@
         <v>42</v>
       </c>
       <c r="F23" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G23" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="H23" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1379,16 +1367,16 @@
         <v>22</v>
       </c>
       <c r="E24" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F24" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G24" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H24" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1405,16 +1393,16 @@
         <v>23</v>
       </c>
       <c r="E25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G25" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H25" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1431,16 +1419,16 @@
         <v>22</v>
       </c>
       <c r="E26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G26" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="H26" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1457,16 +1445,16 @@
         <v>23</v>
       </c>
       <c r="E27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F27" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G27" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H27" t="s">
-        <v>127</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1483,16 +1471,16 @@
         <v>22</v>
       </c>
       <c r="E28" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F28" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G28" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H28" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1509,16 +1497,16 @@
         <v>23</v>
       </c>
       <c r="E29" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F29" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="G29" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H29" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1538,13 +1526,13 @@
         <v>48</v>
       </c>
       <c r="F30" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="G30" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H30" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1564,13 +1552,13 @@
         <v>49</v>
       </c>
       <c r="F31" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="G31" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="H31" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
